--- a/data/trans_dic/P59A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,26</t>
+          <t>3,9; 8,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,69</t>
+          <t>5,69; 10,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,19</t>
+          <t>4,21; 9,33</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 8,74</t>
+          <t>2,09; 9,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 13,18</t>
+          <t>7,23; 12,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,37; 15,02</t>
+          <t>8,46; 14,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,28</t>
+          <t>10,15; 17,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,26; 12,41</t>
+          <t>4,49; 12,92</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,89</t>
+          <t>6,25; 9,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 11,77</t>
+          <t>7,54; 11,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,85; 12,23</t>
+          <t>8,0; 12,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,57; 9,01</t>
+          <t>3,71; 9,14</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>19,98; 28,54</t>
+          <t>20,02; 27,99</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,01; 27,33</t>
+          <t>19,28; 27,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,13; 37,44</t>
+          <t>27,63; 37,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>24,13; 37,28</t>
+          <t>23,94; 37,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>22,5; 33,92</t>
+          <t>23,08; 34,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,34; 36,52</t>
+          <t>25,16; 37,05</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,03; 35,9</t>
+          <t>26,1; 36,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>13,41; 33,37</t>
+          <t>12,86; 32,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,43; 29,54</t>
+          <t>22,32; 28,87</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,32; 29,08</t>
+          <t>22,54; 29,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,77; 35,84</t>
+          <t>28,63; 35,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,65; 32,65</t>
+          <t>20,02; 32,98</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,52; 18,24</t>
+          <t>6,64; 17,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,39; 29,78</t>
+          <t>15,8; 30,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,92; 31,21</t>
+          <t>18,63; 31,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,9; 35,57</t>
+          <t>23,2; 35,54</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,43; 19,62</t>
+          <t>7,22; 19,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,42; 41,43</t>
+          <t>23,28; 40,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,21; 33,39</t>
+          <t>20,39; 33,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>27,16; 38,72</t>
+          <t>26,18; 38,42</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,08</t>
+          <t>8,07; 16,74</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,74; 33,09</t>
+          <t>21,56; 32,4</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 30,5</t>
+          <t>21,14; 30,15</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,51; 35,41</t>
+          <t>26,85; 35,75</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,14; 29,11</t>
+          <t>11,48; 28,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>11,53; 26,44</t>
+          <t>12,03; 27,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 19,06</t>
+          <t>7,76; 18,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,32; 16,54</t>
+          <t>8,35; 16,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,51</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 15,76</t>
+          <t>3,96; 15,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,77; 15,81</t>
+          <t>6,0; 16,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>12,84; 21,44</t>
+          <t>13,07; 21,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 15,07</t>
+          <t>5,95; 14,9</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 19,04</t>
+          <t>9,38; 19,2</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 15,9</t>
+          <t>8,23; 15,4</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,29</t>
+          <t>11,35; 17,63</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,33; 24,72</t>
+          <t>5,07; 25,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,11; 24,88</t>
+          <t>5,03; 23,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 26,54</t>
+          <t>9,89; 25,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,64; 17,26</t>
+          <t>7,84; 17,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,67</t>
+          <t>1,04; 9,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 18,82</t>
+          <t>6,04; 18,96</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,82</t>
+          <t>2,09; 9,65</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 10,71</t>
+          <t>5,08; 10,41</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,66; 12,11</t>
+          <t>3,29; 11,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,94; 17,84</t>
+          <t>6,53; 17,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,93; 14,11</t>
+          <t>6,28; 13,99</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,06; 12,72</t>
+          <t>7,23; 12,68</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,42</t>
+          <t>0,0; 11,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 14,04</t>
+          <t>1,63; 13,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,43; 13,57</t>
+          <t>2,41; 14,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 12,35</t>
+          <t>4,3; 12,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,36</t>
+          <t>0,66; 6,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,76</t>
+          <t>1,22; 4,5</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,02</t>
+          <t>0,0; 3,01</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 7,01</t>
+          <t>1,0; 7,17</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,95</t>
+          <t>0,84; 4,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,35</t>
+          <t>2,82; 6,41</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,35</t>
+          <t>0,0; 11,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,7</t>
+          <t>0,0; 8,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,32; 11,43</t>
+          <t>3,42; 11,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,46</t>
+          <t>0,21; 1,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,34</t>
+          <t>0,0; 2,02</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,05</t>
+          <t>0,25; 3,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 3,5</t>
+          <t>1,17; 3,48</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,76; 15,88</t>
+          <t>11,83; 15,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,58; 17,77</t>
+          <t>13,4; 17,46</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,55; 19,57</t>
+          <t>15,53; 19,69</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,11</t>
+          <t>13,73; 18,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,6; 11,87</t>
+          <t>8,57; 12,13</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,44; 16,12</t>
+          <t>12,4; 16,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,43; 15,92</t>
+          <t>12,37; 16,02</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,05; 14,93</t>
+          <t>11,15; 14,87</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,55; 13,19</t>
+          <t>10,65; 13,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,34; 16,13</t>
+          <t>13,39; 16,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,36; 17,06</t>
+          <t>14,45; 17,11</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,02; 16,07</t>
+          <t>13,01; 15,87</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que vive actualmente en pareja</t>
+          <t>Población que vive actualmente en pareja (tasa de respuesta: 98,5%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18474; 38205</t>
+          <t>18030; 38671</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24307; 45699</t>
+          <t>24300; 46573</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16670; 36386</t>
+          <t>16687; 36949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7925; 34826</t>
+          <t>8314; 39781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31496; 57105</t>
+          <t>31303; 55917</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32090; 57619</t>
+          <t>32432; 57181</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37175; 61813</t>
+          <t>36304; 62303</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>12840; 37448</t>
+          <t>13546; 38997</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>56022; 88607</t>
+          <t>55951; 86188</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60795; 95451</t>
+          <t>61140; 95440</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59169; 92169</t>
+          <t>60289; 92522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>24982; 63077</t>
+          <t>25965; 63985</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88303; 126135</t>
+          <t>88512; 123745</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>86854; 124870</t>
+          <t>88071; 124649</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>108585; 144525</t>
+          <t>106670; 145162</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83122; 128409</t>
+          <t>82469; 127938</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62774; 94614</t>
+          <t>64393; 96482</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70833; 102068</t>
+          <t>70305; 103542</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82689; 114041</t>
+          <t>82917; 114373</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47995; 119444</t>
+          <t>46033; 115929</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>161749; 212946</t>
+          <t>160915; 208133</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164368; 214097</t>
+          <t>165982; 215593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>202452; 252183</t>
+          <t>201466; 248477</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>137993; 229309</t>
+          <t>140595; 231661</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9004; 25202</t>
+          <t>9174; 24040</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25267; 48893</t>
+          <t>25949; 50324</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41896; 69095</t>
+          <t>41247; 69197</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>51494; 79983</t>
+          <t>52163; 79914</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9409; 24842</t>
+          <t>9142; 24908</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33350; 58993</t>
+          <t>33147; 57680</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>36980; 61111</t>
+          <t>37312; 61596</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>51719; 73738</t>
+          <t>49857; 73158</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21990; 45222</t>
+          <t>21371; 44327</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66648; 101456</t>
+          <t>66094; 99342</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87369; 123361</t>
+          <t>85483; 121930</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>110079; 147046</t>
+          <t>111512; 148453</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>9111; 26156</t>
+          <t>10315; 25556</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16117; 36960</t>
+          <t>16811; 37960</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15184; 35231</t>
+          <t>14351; 34789</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21325; 42369</t>
+          <t>21401; 42642</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6702</t>
+          <t>0; 6099</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5964; 20747</t>
+          <t>5212; 20185</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10039; 27496</t>
+          <t>10436; 28426</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>25843; 43166</t>
+          <t>26310; 43482</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11031; 29056</t>
+          <t>11480; 28720</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25265; 51667</t>
+          <t>25458; 52123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>31275; 57021</t>
+          <t>29509; 55227</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51838; 79090</t>
+          <t>51944; 80634</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2809; 13019</t>
+          <t>2670; 13204</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3139; 15295</t>
+          <t>3092; 14618</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10666; 28402</t>
+          <t>10589; 27622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14869; 33592</t>
+          <t>15270; 34370</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>947; 7914</t>
+          <t>945; 8459</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6119; 19245</t>
+          <t>6173; 19385</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3581; 16811</t>
+          <t>3574; 16520</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10359; 21689</t>
+          <t>10275; 21075</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5268; 17438</t>
+          <t>4739; 17082</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11359; 29203</t>
+          <t>10699; 29275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16501; 39236</t>
+          <t>17482; 38920</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28048; 50513</t>
+          <t>28725; 50334</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4265</t>
+          <t>0; 4355</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>950; 7962</t>
+          <t>925; 7782</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1860; 10382</t>
+          <t>1841; 11004</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4674; 13438</t>
+          <t>4680; 13468</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 1770</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>972; 10684</t>
+          <t>962; 10034</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 2020</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2199; 8659</t>
+          <t>2212; 8178</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5080</t>
+          <t>0; 5065</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2926; 14152</t>
+          <t>2019; 14480</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1892; 10990</t>
+          <t>1869; 10549</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8122; 18476</t>
+          <t>8188; 18629</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 6147</t>
+          <t>0; 7527</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2077</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7840</t>
+          <t>0; 7279</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3382; 11656</t>
+          <t>3490; 11784</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 2191</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 7401</t>
+          <t>0; 6377</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 10409</t>
+          <t>0; 10466</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>694; 4617</t>
+          <t>659; 4756</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 6644</t>
+          <t>0; 5575</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 7392</t>
+          <t>0; 6383</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1313; 13544</t>
+          <t>832; 13274</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5083; 14633</t>
+          <t>4910; 14583</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>151556; 204574</t>
+          <t>152374; 203455</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>187924; 245821</t>
+          <t>185313; 241494</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>227296; 286069</t>
+          <t>227067; 287809</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>224744; 295040</t>
+          <t>223772; 297705</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>118904; 164076</t>
+          <t>118514; 167653</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>177179; 229468</t>
+          <t>176522; 230592</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>197988; 253637</t>
+          <t>197057; 255272</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>193613; 261573</t>
+          <t>195437; 260487</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>281649; 352236</t>
+          <t>284463; 353780</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>374364; 452819</t>
+          <t>375886; 456788</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>438777; 521238</t>
+          <t>441393; 522749</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>440373; 543579</t>
+          <t>439869; 536616</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P59A-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P59A-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,9; 8,36</t>
+          <t>3,9; 8,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,69; 10,9</t>
+          <t>5,61; 10,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,21; 9,33</t>
+          <t>4,35; 9,88</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,98</t>
+          <t>2,52; 9,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,91</t>
+          <t>7,31; 13,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,46; 14,91</t>
+          <t>8,5; 14,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 17,42</t>
+          <t>10,45; 17,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,49; 12,92</t>
+          <t>4,48; 12,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,62</t>
+          <t>6,1; 9,62</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 11,77</t>
+          <t>7,53; 11,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,0; 12,28</t>
+          <t>7,98; 12,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 9,14</t>
+          <t>4,0; 9,32</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>20,02; 27,99</t>
+          <t>20,27; 29,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,28; 27,29</t>
+          <t>18,89; 27,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,63; 37,6</t>
+          <t>28,4; 37,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23,94; 37,14</t>
+          <t>22,86; 35,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,08; 34,59</t>
+          <t>22,49; 33,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,16; 37,05</t>
+          <t>24,96; 36,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,1; 36,0</t>
+          <t>25,87; 36,07</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>12,86; 32,39</t>
+          <t>25,12; 36,47</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>22,32; 28,87</t>
+          <t>22,45; 29,17</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>22,54; 29,28</t>
+          <t>22,72; 29,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,63; 35,31</t>
+          <t>28,21; 35,19</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,02; 32,98</t>
+          <t>25,41; 33,98</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,87%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 17,4</t>
+          <t>6,76; 17,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>15,8; 30,65</t>
+          <t>16,42; 30,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,63; 31,25</t>
+          <t>19,51; 32,31</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,2; 35,54</t>
+          <t>24,42; 36,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,22; 19,67</t>
+          <t>6,7; 19,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23,28; 40,51</t>
+          <t>23,39; 40,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,39; 33,66</t>
+          <t>21,05; 34,6</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>26,18; 38,42</t>
+          <t>28,12; 38,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,07; 16,74</t>
+          <t>8,25; 16,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>21,56; 32,4</t>
+          <t>21,08; 32,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>21,14; 30,15</t>
+          <t>21,27; 30,32</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,85; 35,75</t>
+          <t>27,41; 35,85</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,48; 28,44</t>
+          <t>11,13; 28,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,03; 27,16</t>
+          <t>12,16; 27,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,76; 18,82</t>
+          <t>8,48; 19,19</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 16,65</t>
+          <t>8,25; 16,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 6,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,96; 15,33</t>
+          <t>4,02; 15,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,0; 16,35</t>
+          <t>6,06; 15,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,07; 21,6</t>
+          <t>13,71; 21,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 14,9</t>
+          <t>5,78; 14,87</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,38; 19,2</t>
+          <t>9,55; 19,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,23; 15,4</t>
+          <t>8,43; 16,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11,35; 17,63</t>
+          <t>11,86; 17,76</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 25,07</t>
+          <t>5,37; 25,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 23,77</t>
+          <t>5,07; 25,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 25,81</t>
+          <t>9,57; 26,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,84; 17,66</t>
+          <t>8,61; 17,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,27</t>
+          <t>1,05; 8,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 18,96</t>
+          <t>5,93; 19,42</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 9,65</t>
+          <t>1,95; 9,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,41</t>
+          <t>5,36; 10,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,29; 11,87</t>
+          <t>3,55; 12,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,53; 17,88</t>
+          <t>6,93; 17,87</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,28; 13,99</t>
+          <t>6,2; 14,25</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,23; 12,68</t>
+          <t>7,49; 12,97</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>
@@ -1417,22 +1417,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,66</t>
+          <t>0,0; 11,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,63; 13,72</t>
+          <t>1,63; 13,65</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 14,38</t>
+          <t>2,5; 13,27</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,3; 12,38</t>
+          <t>5,39; 15,04</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,91</t>
+          <t>0,67; 7,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,5</t>
+          <t>1,04; 4,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,01</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,0; 7,17</t>
+          <t>1,0; 7,31</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,75</t>
+          <t>0,86; 5,26</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,41</t>
+          <t>3,01; 7,04</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,45</t>
+          <t>0,0; 8,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,08</t>
+          <t>0,0; 7,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,55</t>
+          <t>3,54; 11,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1582,22 +1582,22 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,5</t>
+          <t>0,3; 1,93</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1607,12 +1607,12 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,25; 3,97</t>
+          <t>0,25; 3,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,48</t>
+          <t>1,29; 3,73</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,83; 15,79</t>
+          <t>11,82; 15,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>13,4; 17,46</t>
+          <t>13,31; 17,23</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15,53; 19,69</t>
+          <t>15,46; 19,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13,73; 18,27</t>
+          <t>14,24; 18,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,57; 12,13</t>
+          <t>8,62; 12,06</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,4; 16,2</t>
+          <t>12,24; 16,4</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,37; 16,02</t>
+          <t>12,32; 15,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>11,15; 14,87</t>
+          <t>12,21; 15,13</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,65; 13,25</t>
+          <t>10,65; 13,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13,39; 16,27</t>
+          <t>13,31; 16,12</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14,45; 17,11</t>
+          <t>14,38; 17,07</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,01; 15,87</t>
+          <t>13,8; 16,44</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18564</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>48055</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18030; 38671</t>
+          <t>18023; 38096</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24300; 46573</t>
+          <t>23958; 45240</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16687; 36949</t>
+          <t>17230; 39110</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8314; 39781</t>
+          <t>10264; 39863</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>31303; 55917</t>
+          <t>31655; 57091</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32432; 57181</t>
+          <t>32593; 56041</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36304; 62303</t>
+          <t>37392; 62395</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13546; 38997</t>
+          <t>15611; 43060</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>55951; 86188</t>
+          <t>54633; 86129</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61140; 95440</t>
+          <t>61068; 94439</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60289; 92522</t>
+          <t>60167; 92706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25965; 63985</t>
+          <t>30187; 70370</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>104731</t>
+          <t>109697</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>87627</t>
+          <t>96275</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>192358</t>
+          <t>205971</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>88512; 123745</t>
+          <t>89618; 128804</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>88071; 124649</t>
+          <t>86293; 123939</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106670; 145162</t>
+          <t>109637; 145656</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82469; 127938</t>
+          <t>86812; 135191</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>64393; 96482</t>
+          <t>62743; 92317</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70305; 103542</t>
+          <t>69750; 101155</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>82917; 114373</t>
+          <t>82186; 114577</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>46033; 115929</t>
+          <t>79126; 114890</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>160915; 208133</t>
+          <t>161862; 210302</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165982; 215593</t>
+          <t>167273; 216226</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>201466; 248477</t>
+          <t>198519; 247637</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>140595; 231661</t>
+          <t>176505; 236053</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>65814</t>
+          <t>76133</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62378</t>
+          <t>71321</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>128192</t>
+          <t>147454</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9174; 24040</t>
+          <t>9346; 24047</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25949; 50324</t>
+          <t>26953; 49745</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41247; 69197</t>
+          <t>43191; 71548</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52163; 79914</t>
+          <t>61396; 92240</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>9142; 24908</t>
+          <t>8480; 24552</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>33147; 57680</t>
+          <t>33299; 57828</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37312; 61596</t>
+          <t>38520; 63326</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49857; 73158</t>
+          <t>60662; 83496</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>21371; 44327</t>
+          <t>21837; 42861</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66094; 99342</t>
+          <t>64620; 99073</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85483; 121930</t>
+          <t>86027; 122614</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>111512; 148453</t>
+          <t>128073; 167464</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30524</t>
+          <t>32455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>34121</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>64646</t>
+          <t>71621</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10315; 25556</t>
+          <t>9995; 25547</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>16811; 37960</t>
+          <t>16991; 38193</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14351; 34789</t>
+          <t>15681; 35472</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>21401; 42642</t>
+          <t>22257; 44114</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 6099</t>
+          <t>0; 7144</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5212; 20185</t>
+          <t>5286; 20870</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10436; 28426</t>
+          <t>10542; 27160</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26310; 43482</t>
+          <t>30445; 48467</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11480; 28720</t>
+          <t>11137; 28659</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>25458; 52123</t>
+          <t>25927; 51933</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29509; 55227</t>
+          <t>30231; 58194</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>51944; 80634</t>
+          <t>58314; 87338</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23625</t>
+          <t>25988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>15096</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>38721</t>
+          <t>43710</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2670; 13204</t>
+          <t>2827; 13424</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3092; 14618</t>
+          <t>3120; 15641</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>10589; 27622</t>
+          <t>10243; 28360</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15270; 34370</t>
+          <t>17941; 36621</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>945; 8459</t>
+          <t>955; 8057</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6173; 19385</t>
+          <t>6060; 19853</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3574; 16520</t>
+          <t>3331; 16131</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10275; 21075</t>
+          <t>12207; 24967</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4739; 17082</t>
+          <t>5106; 17556</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10699; 29275</t>
+          <t>11345; 29258</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17482; 38920</t>
+          <t>17257; 39626</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>28725; 50334</t>
+          <t>32652; 56556</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>11055</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4430</t>
+          <t>4705</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>12849</t>
+          <t>15760</t>
         </is>
       </c>
     </row>
@@ -3108,22 +3108,22 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 4355</t>
+          <t>0; 4327</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>925; 7782</t>
+          <t>925; 7741</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1841; 11004</t>
+          <t>1912; 10151</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4680; 13468</t>
+          <t>6536; 18251</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>962; 10034</t>
+          <t>971; 11508</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3143,27 +3143,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2212; 8178</t>
+          <t>2052; 8143</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 5065</t>
+          <t>0; 4251</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2019; 14480</t>
+          <t>2017; 14766</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1869; 10549</t>
+          <t>1903; 11669</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8188; 18629</t>
+          <t>9604; 22481</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>7668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>2646</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>8768</t>
+          <t>10313</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 7527</t>
+          <t>0; 5698</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 7279</t>
+          <t>0; 6866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3490; 11784</t>
+          <t>3953; 13203</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3341,37 +3341,37 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 6377</t>
+          <t>0; 8073</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 10466</t>
+          <t>0; 10680</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>659; 4756</t>
+          <t>1029; 6639</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 5575</t>
+          <t>0; 6382</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>0; 6383</t>
+          <t>0; 6390</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>832; 13274</t>
+          <t>827; 12776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>4910; 14583</t>
+          <t>5860; 16994</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>152374; 203455</t>
+          <t>152328; 203813</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>185313; 241494</t>
+          <t>184121; 238355</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>227067; 287809</t>
+          <t>226086; 284564</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>223772; 297705</t>
+          <t>249020; 325349</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>118514; 167653</t>
+          <t>119166; 166694</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>176522; 230592</t>
+          <t>174290; 233501</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>197057; 255272</t>
+          <t>196240; 254437</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>195437; 260487</t>
+          <t>228445; 283176</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>284463; 353780</t>
+          <t>284529; 357341</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>375886; 456788</t>
+          <t>373746; 452634</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>441393; 522749</t>
+          <t>439242; 521488</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>439869; 536616</t>
+          <t>499586; 595084</t>
         </is>
       </c>
     </row>
